--- a/safety_inspection_forms/023_stadium_security_assessment_form--safety_inspection_forms.xlsx
+++ b/safety_inspection_forms/023_stadium_security_assessment_form--safety_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1088,8 +1088,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'cctv'}</t>
+          <t>cctv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'CCTV'}</t>
+          <t>CCTV</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'emergency_response_plan'}</t>
+          <t>emergency_response_plan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Emergency Response Plan'}</t>
+          <t>Emergency Response Plan</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'first_aid_kit'}</t>
+          <t>first_aid_kit</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'First Aid Kit'}</t>
+          <t>First Aid Kit</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'locks_and_keys'}</t>
+          <t>locks_and_keys</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Locks and Keys'}</t>
+          <t>Locks and Keys</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'secure_communication'}</t>
+          <t>secure_communication</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Secure Communication'}</t>
+          <t>Secure Communication</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'access_control_system'}</t>
+          <t>access_control_system</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Access Control System'}</t>
+          <t>Access Control System</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'alarm_system'}</t>
+          <t>alarm_system</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Alarm System'}</t>
+          <t>Alarm System</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'other_(please_describe)'}</t>
+          <t>other_(please_describe)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Other (please describe)'}</t>
+          <t>Other (please describe)</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'1-2',_'label':_'not_very_secure'}</t>
+          <t>not_very_secure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': '1-2', 'label': 'Not Very Secure'}</t>
+          <t>Not Very Secure</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'2-3',_'label':_'somewhat_secure'}</t>
+          <t>somewhat_secure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': '2-3', 'label': 'Somewhat Secure'}</t>
+          <t>Somewhat Secure</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'4-5',_'label':_'very_secure'}</t>
+          <t>very_secure</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': '4-5', 'label': 'Very Secure'}</t>
+          <t>Very Secure</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'extremely_secure'}</t>
+          <t>extremely_secure</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Extremely Secure'}</t>
+          <t>Extremely Secure</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'in_person',_'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'In Person', 'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'via_email',_'label':_'via_email'}</t>
+          <t>via_email</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Via Email', 'label': 'Via Email'}</t>
+          <t>Via Email</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'online_submission',_'label':_'online_submission'}</t>
+          <t>online_submission</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Online Submission', 'label': 'Online Submission'}</t>
+          <t>Online Submission</t>
         </is>
       </c>
     </row>
